--- a/kanban_system/output/library_linked/以色列法规清单.xlsx
+++ b/kanban_system/output/library_linked/以色列法规清单.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="以色列" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="草案" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="以色列" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="草案" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="更新" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'以色列'!$A$1:$Y$1</definedName>
@@ -3467,6 +3467,11 @@
           <t>(EU) 2018/858: mandatory for new TA from 09.2020(in accordance with the relevant implementation dates)</t>
         </is>
       </c>
+      <c r="Z28" s="21" t="inlineStr">
+        <is>
+          <t>INS-2022-005 中欧汽车认证与法规比较</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
@@ -3574,6 +3579,11 @@
       <c r="Y29" s="14" t="inlineStr">
         <is>
           <t>(EU) 2019/2144 - GSR: mandatory   in accordance with the relevant implementation dates</t>
+        </is>
+      </c>
+      <c r="Z29" s="21" t="inlineStr">
+        <is>
+          <t>INS-2026-001 (EU) 2021/1958 ISA 智能速度辅助系统</t>
         </is>
       </c>
     </row>
